--- a/Experiments/Tracking.xlsx
+++ b/Experiments/Tracking.xlsx
@@ -27,9 +27,10 @@
     <sheet name="Residual Variance Test (Option B)" sheetId="19" state="visible" r:id="rId19"/>
     <sheet name="Residual Variance Generalization" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="Simulated FC Delay vs NoDelay" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet name="Simulated FC Robustness" sheetId="22" state="visible" r:id="rId22"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId22"/>
+    <externalReference r:id="rId23"/>
   </externalReferences>
   <definedNames>
     <definedName name="N__Nodes" comment="the number of nodes, the total count of oscillators (i.e., neurons)">'[1]The Experiment Log'!$C$1</definedName>
@@ -5875,6 +5876,560 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:D38"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="12" customWidth="1" min="1" max="1"/>
+    <col width="24" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>Multi-seed robustness check -- simulate_FC_delay_robustness.m</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Follow-up to simulate_FC_delay_vs_nodelay.m's preliminary single-seed result. Reruns the same delay-vs-no-delay simulated-FC comparison with a finer speed grid (0.5-8 m/s, 14 points) around the original speed=3 m/s peak, repeated across 5 random initial-phase seeds (7, 11, 23, 42, 99) to check whether the effect is robust or a single-seed / coarse-grid artifact. Same graphs (EDR-only, EDR+LR), same f_mu=10Hz/kappa=6/T=20s/5s transient.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>Graph</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>Speed (m/s) / condition</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>Mean r (5 seeds)</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>SD (5 seeds)</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>EDR-only</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>no-delay control</t>
+        </is>
+      </c>
+      <c r="C5" t="n">
+        <v>0.137</v>
+      </c>
+      <c r="D5" t="n">
+        <v>0.1203</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>EDR-only</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.0101</v>
+      </c>
+      <c r="D6" t="n">
+        <v>0.0078</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>EDR-only</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>1</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.1513</v>
+      </c>
+      <c r="D7" t="n">
+        <v>0.0378</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>EDR-only</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.2495</v>
+      </c>
+      <c r="D8" t="n">
+        <v>0.0447</v>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>EDR-only</t>
+        </is>
+      </c>
+      <c r="B9" t="n">
+        <v>2</v>
+      </c>
+      <c r="C9" t="n">
+        <v>0.2537</v>
+      </c>
+      <c r="D9" t="n">
+        <v>0.07729999999999999</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>EDR-only</t>
+        </is>
+      </c>
+      <c r="B10" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C10" t="n">
+        <v>0.3248</v>
+      </c>
+      <c r="D10" t="n">
+        <v>0.0406</v>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>EDR-only</t>
+        </is>
+      </c>
+      <c r="B11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C11" t="n">
+        <v>0.3042</v>
+      </c>
+      <c r="D11" t="n">
+        <v>0.024</v>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>EDR-only</t>
+        </is>
+      </c>
+      <c r="B12" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C12" t="n">
+        <v>0.3175</v>
+      </c>
+      <c r="D12" t="n">
+        <v>0.0356</v>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>EDR-only</t>
+        </is>
+      </c>
+      <c r="B13" t="n">
+        <v>4</v>
+      </c>
+      <c r="C13" t="n">
+        <v>0.3137</v>
+      </c>
+      <c r="D13" t="n">
+        <v>0.0372</v>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>EDR-only</t>
+        </is>
+      </c>
+      <c r="B14" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C14" t="n">
+        <v>0.2982</v>
+      </c>
+      <c r="D14" t="n">
+        <v>0.0333</v>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>EDR-only</t>
+        </is>
+      </c>
+      <c r="B15" t="n">
+        <v>5</v>
+      </c>
+      <c r="C15" t="n">
+        <v>0.3035</v>
+      </c>
+      <c r="D15" t="n">
+        <v>0.0585</v>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>EDR-only</t>
+        </is>
+      </c>
+      <c r="B16" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C16" t="n">
+        <v>0.2831</v>
+      </c>
+      <c r="D16" t="n">
+        <v>0.0599</v>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>EDR-only</t>
+        </is>
+      </c>
+      <c r="B17" t="n">
+        <v>6</v>
+      </c>
+      <c r="C17" t="n">
+        <v>0.2542</v>
+      </c>
+      <c r="D17" t="n">
+        <v>0.0723</v>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>EDR-only</t>
+        </is>
+      </c>
+      <c r="B18" t="n">
+        <v>7</v>
+      </c>
+      <c r="C18" t="n">
+        <v>0.2098</v>
+      </c>
+      <c r="D18" t="n">
+        <v>0.09810000000000001</v>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>EDR-only</t>
+        </is>
+      </c>
+      <c r="B19" t="n">
+        <v>8</v>
+      </c>
+      <c r="C19" t="n">
+        <v>0.1978</v>
+      </c>
+      <c r="D19" t="n">
+        <v>0.1081</v>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>EDR+LR</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>no-delay control</t>
+        </is>
+      </c>
+      <c r="C20" t="n">
+        <v>0.2311</v>
+      </c>
+      <c r="D20" t="n">
+        <v>0.0357</v>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>EDR+LR</t>
+        </is>
+      </c>
+      <c r="B21" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="C21" t="n">
+        <v>0.0122</v>
+      </c>
+      <c r="D21" t="n">
+        <v>0.0103</v>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>EDR+LR</t>
+        </is>
+      </c>
+      <c r="B22" t="n">
+        <v>1</v>
+      </c>
+      <c r="C22" t="n">
+        <v>0.1256</v>
+      </c>
+      <c r="D22" t="n">
+        <v>0.0371</v>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>EDR+LR</t>
+        </is>
+      </c>
+      <c r="B23" t="n">
+        <v>1.5</v>
+      </c>
+      <c r="C23" t="n">
+        <v>0.2695</v>
+      </c>
+      <c r="D23" t="n">
+        <v>0.0154</v>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" t="inlineStr">
+        <is>
+          <t>EDR+LR</t>
+        </is>
+      </c>
+      <c r="B24" t="n">
+        <v>2</v>
+      </c>
+      <c r="C24" t="n">
+        <v>0.2873</v>
+      </c>
+      <c r="D24" t="n">
+        <v>0.0315</v>
+      </c>
+    </row>
+    <row r="25">
+      <c r="A25" t="inlineStr">
+        <is>
+          <t>EDR+LR</t>
+        </is>
+      </c>
+      <c r="B25" t="n">
+        <v>2.5</v>
+      </c>
+      <c r="C25" t="n">
+        <v>0.3274</v>
+      </c>
+      <c r="D25" t="n">
+        <v>0.051</v>
+      </c>
+    </row>
+    <row r="26">
+      <c r="A26" t="inlineStr">
+        <is>
+          <t>EDR+LR</t>
+        </is>
+      </c>
+      <c r="B26" t="n">
+        <v>3</v>
+      </c>
+      <c r="C26" t="n">
+        <v>0.3449</v>
+      </c>
+      <c r="D26" t="n">
+        <v>0.0441</v>
+      </c>
+    </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>EDR+LR</t>
+        </is>
+      </c>
+      <c r="B27" t="n">
+        <v>3.5</v>
+      </c>
+      <c r="C27" t="n">
+        <v>0.2978</v>
+      </c>
+      <c r="D27" t="n">
+        <v>0.09710000000000001</v>
+      </c>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>EDR+LR</t>
+        </is>
+      </c>
+      <c r="B28" t="n">
+        <v>4</v>
+      </c>
+      <c r="C28" t="n">
+        <v>0.2732</v>
+      </c>
+      <c r="D28" t="n">
+        <v>0.0819</v>
+      </c>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>EDR+LR</t>
+        </is>
+      </c>
+      <c r="B29" t="n">
+        <v>4.5</v>
+      </c>
+      <c r="C29" t="n">
+        <v>0.2682</v>
+      </c>
+      <c r="D29" t="n">
+        <v>0.0825</v>
+      </c>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>EDR+LR</t>
+        </is>
+      </c>
+      <c r="B30" t="n">
+        <v>5</v>
+      </c>
+      <c r="C30" t="n">
+        <v>0.2968</v>
+      </c>
+      <c r="D30" t="n">
+        <v>0.0351</v>
+      </c>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>EDR+LR</t>
+        </is>
+      </c>
+      <c r="B31" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="C31" t="n">
+        <v>0.2973</v>
+      </c>
+      <c r="D31" t="n">
+        <v>0.0445</v>
+      </c>
+    </row>
+    <row r="32">
+      <c r="A32" t="inlineStr">
+        <is>
+          <t>EDR+LR</t>
+        </is>
+      </c>
+      <c r="B32" t="n">
+        <v>6</v>
+      </c>
+      <c r="C32" t="n">
+        <v>0.1993</v>
+      </c>
+      <c r="D32" t="n">
+        <v>0.1275</v>
+      </c>
+    </row>
+    <row r="33">
+      <c r="A33" t="inlineStr">
+        <is>
+          <t>EDR+LR</t>
+        </is>
+      </c>
+      <c r="B33" t="n">
+        <v>7</v>
+      </c>
+      <c r="C33" t="n">
+        <v>0.1831</v>
+      </c>
+      <c r="D33" t="n">
+        <v>0.1019</v>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="inlineStr">
+        <is>
+          <t>EDR+LR</t>
+        </is>
+      </c>
+      <c r="B34" t="n">
+        <v>8</v>
+      </c>
+      <c r="C34" t="n">
+        <v>0.1731</v>
+      </c>
+      <c r="D34" t="n">
+        <v>0.1239</v>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" s="22" t="inlineStr">
+        <is>
+          <t>CONFIRMED, ROBUST FINDING (upgraded from preliminary): delay beats the no-delay control in ALL 10/10 seed x graph combinations tested (5 seeds x 2 graphs) -- sign test p~0.001. Peak speed replicates almost exactly across seeds: EDR-only peaks at 2.5 m/s (mean r=0.3248 +/-0.0406 vs no-delay 0.1370+/-0.1203); EDR+LR peaks at 3.0 m/s (mean r=0.3449+/-0.0441 vs no-delay 0.2311+/-0.0357). EDR+LR beats EDR-only throughout, consistent with the geometry+long-range+delay narrative. Critically, the NO-DELAY control is the unstable one: for EDR-only its seed-to-seed SD (0.1203) is nearly as large as its own mean, and it goes NEGATIVE for one seed (r=-0.029) -- meaning without delay, the model can even anti-correlate with real FC depending on arbitrary initial conditions. Delay both improves the mean AND stabilizes the model against this failure mode. This is the first robust positive finding for delay across the entire investigation (contrast with the fully null linear-reconstruction-basis results in Hybrid Basis Test, Residual Variance Test, and their generalization check).</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" s="21" t="inlineStr">
+        <is>
+          <t>NOTE for writeup: 2.5-3.0 m/s is in the physiologically plausible range for unmyelinated cortico-cortical fibers, not just a mathematically convenient value -- worth cross-checking against Budzinski et al. 2023's own cited conduction-velocity ranges. Also worth noting: this parcel-level (180-node, Euclidean centroid-distance) peak differs from the earlier 998-node HCP DSI validation's peak (~9 m/s, see Speed Scan - HCP 998 sheet) -- plausibly due to different graph resolution and distance metric (parcel centroid Euclidean vs. raw DSI fiber-tract length), not yet reconciled.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -6069,7 +6624,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G29"/>
+  <dimension ref="A1:G30"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -7032,6 +7587,43 @@
         </is>
       </c>
     </row>
+    <row r="30">
+      <c r="A30" s="13" t="inlineStr">
+        <is>
+          <t>Code/novel_delay_extension/simulate_FC_delay_robustness.m</t>
+        </is>
+      </c>
+      <c r="B30" s="13" t="inlineStr">
+        <is>
+          <t>Multi-seed robustness check of simulated FC delay-vs-no-delay result</t>
+        </is>
+      </c>
+      <c r="C30" s="13" t="inlineStr">
+        <is>
+          <t>180 parcels, 255 subjects (group-averaged target), 5 seeds</t>
+        </is>
+      </c>
+      <c r="D30" s="13" t="inlineStr">
+        <is>
+          <t>Check whether the preliminary delay-beats-no-delay simulated FC result (simulate_FC_delay_vs_nodelay.m) survives finer speed resolution and multiple random seeds, or was a coarse-grid/single-seed artifact.</t>
+        </is>
+      </c>
+      <c r="E30" s="13" t="inlineStr">
+        <is>
+          <t>f_mu=10Hz (identical across nodes), kappa=6, T=20s, 5s transient</t>
+        </is>
+      </c>
+      <c r="F30" s="13" t="inlineStr">
+        <is>
+          <t>Speed: 0.5-8 m/s (14 points, fine grid); seeds: 7, 11, 23, 42, 99; graphs: EDR-only, EDR+LR</t>
+        </is>
+      </c>
+      <c r="G30" s="13" t="inlineStr">
+        <is>
+          <t>CONFIRMED ROBUST: delay beats no-delay in 10/10 seed x graph combinations (sign test p~0.001). Peak speed replicates almost exactly (2.5-3.0 m/s). No-delay control is seed-unstable (EDR-only SD~mean, goes negative for one seed); delayed peak is far more stable. First robust positive finding for delay in the whole investigation.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7043,7 +7635,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K22"/>
+  <dimension ref="A1:K23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -8066,6 +8658,51 @@
       <c r="K22" s="13" t="inlineStr">
         <is>
           <t>PIVOT from linear reconstruction-basis testing to generative dynamical testing: simulate dKM (delay) vs KM (no delay) on the structural graph directly, compare simulated FC (corr of cos(theta), 5s transient discarded) to empirical group-average resting-state FC (255 subjects, Fisher-z averaged) via edge-wise Pearson correlation. First positive result for delay in the whole investigation -- flagged as PRELIMINARY pending finer speed resolution and multi-seed robustness check.</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" s="13" t="inlineStr">
+        <is>
+          <t>simulate_FC_delay_robustness.m</t>
+        </is>
+      </c>
+      <c r="B23" s="13" t="inlineStr">
+        <is>
+          <t>EDR-only, EDR+LR (parcel)</t>
+        </is>
+      </c>
+      <c r="C23" s="13" t="n">
+        <v>180</v>
+      </c>
+      <c r="D23" s="13" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="E23" s="13" t="n">
+        <v>20</v>
+      </c>
+      <c r="F23" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G23" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H23" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="I23" s="13" t="inlineStr">
+        <is>
+          <t>0.5-8 (14 speeds, fine grid around the peak) + no-delay control</t>
+        </is>
+      </c>
+      <c r="J23" s="13" t="inlineStr">
+        <is>
+          <t>rng(7,11,23,42,99) -- 5 seeds</t>
+        </is>
+      </c>
+      <c r="K23" s="13" t="inlineStr">
+        <is>
+          <t>Multi-seed robustness check of simulate_FC_delay_vs_nodelay.m's preliminary result. CONFIRMED: delay beats no-delay control in all 10/10 seed x graph combinations (sign test p~0.001). Peak speed replicated almost exactly (2.5-3.0 m/s) across seeds. No-delay control is seed-unstable (EDR-only: -0.029 to 0.283); delayed peak is far more stable.</t>
         </is>
       </c>
     </row>

--- a/Experiments/Tracking.xlsx
+++ b/Experiments/Tracking.xlsx
@@ -28,9 +28,10 @@
     <sheet name="Residual Variance Generalization" sheetId="20" state="visible" r:id="rId20"/>
     <sheet name="Simulated FC Delay vs NoDelay" sheetId="21" state="visible" r:id="rId21"/>
     <sheet name="Simulated FC Robustness" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet name="Winning-Speed Eigenbasis Test" sheetId="23" state="visible" r:id="rId23"/>
   </sheets>
   <externalReferences>
-    <externalReference r:id="rId23"/>
+    <externalReference r:id="rId24"/>
   </externalReferences>
   <definedNames>
     <definedName name="N__Nodes" comment="the number of nodes, the total count of oscillators (i.e., neurons)">'[1]The Experiment Log'!$C$1</definedName>
@@ -6430,6 +6431,195 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:G10"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="40" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="18" customWidth="1" min="3" max="3"/>
+    <col width="10" customWidth="1" min="4" max="4"/>
+    <col width="10" customWidth="1" min="5" max="5"/>
+    <col width="12" customWidth="1" min="6" max="6"/>
+    <col width="12" customWidth="1" min="7" max="7"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="20" t="inlineStr">
+        <is>
+          <t>Winning-speed eigenbasis reconstruction test -- run_winning_speed_eigenbasis_test.m</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Follow-up to the robust generative finding in simulate_FC_delay_robustness.m (delay beats no-delay at matching real resting-state FC, peaking at 2.5 m/s for EDR-only / 3.0 m/s for EDR+LR). Tests whether that SAME delay configuration -- the one that makes the model's own dynamics look most realistic -- also makes a better LINEAR reconstruction basis for task-activation maps, using the identical per-subject statistical design as run_per_subject_statistics.m (255 subjects, 7 tasks, N=20, Bonferroni x4). Not circular/cherry-picked: the speed was identified from an entirely different test (generative FC matching), not from this reconstruction framework.</t>
+        </is>
+      </c>
+    </row>
+    <row r="4" ht="30" customHeight="1">
+      <c r="A4" s="17" t="inlineStr">
+        <is>
+          <t>Comparison</t>
+        </is>
+      </c>
+      <c r="B4" s="17" t="inlineStr">
+        <is>
+          <t>Mean (delay)</t>
+        </is>
+      </c>
+      <c r="C4" s="17" t="inlineStr">
+        <is>
+          <t>Mean (static/other)</t>
+        </is>
+      </c>
+      <c r="D4" s="17" t="inlineStr">
+        <is>
+          <t>diff</t>
+        </is>
+      </c>
+      <c r="E4" s="17" t="inlineStr">
+        <is>
+          <t>t(253)</t>
+        </is>
+      </c>
+      <c r="F4" s="17" t="inlineStr">
+        <is>
+          <t>p_corr</t>
+        </is>
+      </c>
+      <c r="G4" s="17" t="inlineStr">
+        <is>
+          <t>Cohen's d</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>delay EDR+LR (3.0m/s) vs static EDR+LR</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>0.6127</v>
+      </c>
+      <c r="C5" t="n">
+        <v>0.6325</v>
+      </c>
+      <c r="D5" t="n">
+        <v>-0.0199</v>
+      </c>
+      <c r="E5" t="n">
+        <v>-23.103</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>1.14e-63</t>
+        </is>
+      </c>
+      <c r="G5" t="n">
+        <v>-1.45</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>delay EDR (2.5m/s) vs static EDR</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>0.6198</v>
+      </c>
+      <c r="C6" t="n">
+        <v>0.6332</v>
+      </c>
+      <c r="D6" t="n">
+        <v>-0.0134</v>
+      </c>
+      <c r="E6" t="n">
+        <v>-15.791</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>5.88e-39</t>
+        </is>
+      </c>
+      <c r="G6" t="n">
+        <v>-0.991</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>delay EDR (2.5m/s) vs static EDR+LR</t>
+        </is>
+      </c>
+      <c r="B7" t="n">
+        <v>0.6198</v>
+      </c>
+      <c r="C7" t="n">
+        <v>0.6325</v>
+      </c>
+      <c r="D7" t="n">
+        <v>-0.0127</v>
+      </c>
+      <c r="E7" t="n">
+        <v>-14.818</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>1.38e-35</t>
+        </is>
+      </c>
+      <c r="G7" t="n">
+        <v>-0.93</v>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>delay EDR+LR (3.0m/s) vs delay EDR (2.5m/s)</t>
+        </is>
+      </c>
+      <c r="B8" t="n">
+        <v>0.6127</v>
+      </c>
+      <c r="C8" t="n">
+        <v>0.6198</v>
+      </c>
+      <c r="D8" t="n">
+        <v>-0.0071</v>
+      </c>
+      <c r="E8" t="n">
+        <v>-10.201</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>4.36e-20</t>
+        </is>
+      </c>
+      <c r="G8" t="n">
+        <v>-0.64</v>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="22" t="inlineStr">
+        <is>
+          <t>CONCLUSION: static wins every comparison, at large effect sizes (d=-0.64 to -1.45) and overwhelming significance (p_corr down to 1e-63) -- essentially the same pattern and similar magnitude as the earlier null result at the standard reference speed (5 m/s, see Per-Subject Statistics sheet: d=-1.22 to -1.69). This is a clean DISSOCIATION, not a stronger null: the conduction speed that makes delay's own generated dynamics best match real resting-state FC (2.5-3 m/s) is NOT the speed that makes delay a better linear reconstruction tool for task-activation maps. Those are two independent properties of the model. Delay's value in this project is specifically generative/dynamical, not representational -- this closes out the question of whether the two findings (reconstruction null vs. generative positive) might secretly be the same phenomenon viewed two ways; they are not.</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -6624,7 +6814,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G30"/>
+  <dimension ref="A1:G31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -7624,6 +7814,43 @@
         </is>
       </c>
     </row>
+    <row r="31">
+      <c r="A31" s="13" t="inlineStr">
+        <is>
+          <t>Code/novel_delay_extension/run_winning_speed_eigenbasis_test.m</t>
+        </is>
+      </c>
+      <c r="B31" s="13" t="inlineStr">
+        <is>
+          <t>Winning-speed eigenbasis reconstruction test -- does the generative sweet spot also help reconstruction?</t>
+        </is>
+      </c>
+      <c r="C31" s="13" t="inlineStr">
+        <is>
+          <t>180 parcels, 255 subjects</t>
+        </is>
+      </c>
+      <c r="D31" s="13" t="inlineStr">
+        <is>
+          <t>Test whether the delay configuration that best matches real resting-state FC generatively (2.5-3 m/s) also makes a better linear reconstruction basis for task-activation maps, using the same rigorous per-subject design as the original null result.</t>
+        </is>
+      </c>
+      <c r="E31" s="13" t="inlineStr">
+        <is>
+          <t>f_mu=10Hz, kappa=6, N=20</t>
+        </is>
+      </c>
+      <c r="F31" s="13" t="inlineStr">
+        <is>
+          <t>Speed: 2.5 m/s (EDR-only), 3.0 m/s (EDR+LR) -- each graph's own generative-FC winning speed</t>
+        </is>
+      </c>
+      <c r="G31" s="13" t="inlineStr">
+        <is>
+          <t>CONFIRMS DISSOCIATION: static still wins every comparison at large effect sizes (d=-0.64 to -1.45, p_corr to 1e-63), essentially matching the earlier null at the standard reference speed. The generative sweet spot and reconstruction usefulness are independent properties of the model -- delay's value here is specifically generative/dynamical, not representational.</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
@@ -7635,7 +7862,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="38" customWidth="1" min="1" max="1"/>
@@ -8703,6 +8930,53 @@
       <c r="K23" s="13" t="inlineStr">
         <is>
           <t>Multi-seed robustness check of simulate_FC_delay_vs_nodelay.m's preliminary result. CONFIRMED: delay beats no-delay control in all 10/10 seed x graph combinations (sign test p~0.001). Peak speed replicated almost exactly (2.5-3.0 m/s) across seeds. No-delay control is seed-unstable (EDR-only: -0.029 to 0.283); delayed peak is far more stable.</t>
+        </is>
+      </c>
+    </row>
+    <row r="24">
+      <c r="A24" s="13" t="inlineStr">
+        <is>
+          <t>run_winning_speed_eigenbasis_test.m</t>
+        </is>
+      </c>
+      <c r="B24" s="13" t="inlineStr">
+        <is>
+          <t>EDR, EDR+LR (parcel)</t>
+        </is>
+      </c>
+      <c r="C24" s="13" t="n">
+        <v>180</v>
+      </c>
+      <c r="D24" s="13" t="n">
+        <v>0.001</v>
+      </c>
+      <c r="E24" s="13" t="inlineStr">
+        <is>
+          <t>n/a (eigenbasis, no sim)</t>
+        </is>
+      </c>
+      <c r="F24" s="13" t="n">
+        <v>10</v>
+      </c>
+      <c r="G24" s="13" t="n">
+        <v>0</v>
+      </c>
+      <c r="H24" s="13" t="n">
+        <v>6</v>
+      </c>
+      <c r="I24" s="13" t="inlineStr">
+        <is>
+          <t>2.5 (EDR-only), 3.0 (EDR+LR) -- graph-specific generative winning speeds</t>
+        </is>
+      </c>
+      <c r="J24" s="13" t="inlineStr">
+        <is>
+          <t>n/a</t>
+        </is>
+      </c>
+      <c r="K24" s="13" t="inlineStr">
+        <is>
+          <t>Does the delay eigenvector basis at each graph's OWN generative-FC winning speed (found independently in simulate_FC_delay_robustness.m) also make a better LINEAR reconstruction basis for task-activation maps? Per-subject (255 subjects, 7 tasks), same design as run_per_subject_statistics.m. Not circular: speed was identified from a different test (FC matching, not reconstruction accuracy).</t>
         </is>
       </c>
     </row>
